--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484776_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484776_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>U. ZAMORA MANA</t>
+          <t>D. CAZORLA ZARAGOZI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.3606</v>
+        <v>6.7252</v>
       </c>
       <c r="E2" t="n">
-        <v>4.7958</v>
+        <v>6.3027</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5647</v>
+        <v>0.4225</v>
       </c>
       <c r="G2" t="n">
-        <v>1.7382</v>
+        <v>4.2285</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9548</v>
+        <v>0.2825</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7835</v>
+        <v>3.946</v>
       </c>
       <c r="J2" t="n">
-        <v>3.2184</v>
+        <v>4.9718</v>
       </c>
       <c r="K2" t="n">
-        <v>1.7859</v>
+        <v>0.5283</v>
       </c>
       <c r="L2" t="n">
-        <v>1.4325</v>
+        <v>4.4435</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.4801</v>
+        <v>-0.7433</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.8310999999999999</v>
+        <v>-0.2457</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.649</v>
+        <v>-0.4976</v>
       </c>
       <c r="P2" t="n">
-        <v>0.7548</v>
+        <v>1.1322</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.9435</v>
+        <v>-0.1887</v>
       </c>
       <c r="R2" t="n">
-        <v>1.6983</v>
+        <v>1.3209</v>
       </c>
       <c r="S2" t="n">
-        <v>1.6789</v>
+        <v>-0.5033</v>
       </c>
       <c r="T2" t="n">
-        <v>0.974</v>
+        <v>-0.3482</v>
       </c>
       <c r="U2" t="n">
-        <v>0.705</v>
+        <v>-0.1551</v>
       </c>
       <c r="V2" t="n">
-        <v>2.1886</v>
+        <v>1.8678</v>
       </c>
       <c r="W2" t="n">
-        <v>1.547</v>
+        <v>1.8678</v>
       </c>
       <c r="X2" t="n">
-        <v>0.6415999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. CAZORLA ZARAGOZI</t>
+          <t>U. ZAMORA MANA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.0075</v>
+        <v>4.8836</v>
       </c>
       <c r="E3" t="n">
-        <v>6.0877</v>
+        <v>3.8215</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0801</v>
+        <v>1.0621</v>
       </c>
       <c r="G3" t="n">
-        <v>4.2285</v>
+        <v>1.7382</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2825</v>
+        <v>0.9548</v>
       </c>
       <c r="I3" t="n">
-        <v>3.946</v>
+        <v>0.7835</v>
       </c>
       <c r="J3" t="n">
-        <v>4.9718</v>
+        <v>3.2184</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5283</v>
+        <v>1.7859</v>
       </c>
       <c r="L3" t="n">
-        <v>4.4435</v>
+        <v>1.4325</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.7433</v>
+        <v>-1.4801</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2457</v>
+        <v>-0.8310999999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.4976</v>
+        <v>-0.649</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1322</v>
+        <v>0.7548</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.1887</v>
+        <v>-0.9435</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3209</v>
+        <v>1.6983</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.221</v>
+        <v>0.2019</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5632</v>
+        <v>-0.0004</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6578000000000001</v>
+        <v>0.2023</v>
       </c>
       <c r="V3" t="n">
-        <v>1.8678</v>
+        <v>2.1886</v>
       </c>
       <c r="W3" t="n">
-        <v>1.8678</v>
+        <v>1.547</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.6415999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.0477</v>
+        <v>3.2891</v>
       </c>
       <c r="E4" t="n">
-        <v>1.4664</v>
+        <v>1.6814</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5813</v>
+        <v>1.6077</v>
       </c>
       <c r="G4" t="n">
         <v>0.2535</v>
@@ -766,13 +766,13 @@
         <v>1.5096</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7154</v>
+        <v>-0.4739</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5632</v>
+        <v>-0.3482</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1522</v>
+        <v>-0.1257</v>
       </c>
       <c r="V4" t="n">
         <v>2.1886</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5938</v>
+        <v>2.0385</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1262</v>
+        <v>2.4386</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5324</v>
+        <v>-0.4001</v>
       </c>
       <c r="G5" t="n">
         <v>2.013</v>
@@ -844,13 +844,13 @@
         <v>1.5096</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9852</v>
+        <v>-0.5405</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0335</v>
+        <v>-0.7211</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0483</v>
+        <v>0.1805</v>
       </c>
       <c r="V5" t="n">
         <v>0.9434</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.262</v>
+        <v>0.351</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2931</v>
+        <v>0.488</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0311</v>
+        <v>-0.1369</v>
       </c>
       <c r="G7" t="n">
         <v>0.5957</v>
@@ -1000,13 +1000,13 @@
         <v>0.9435</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.485</v>
+        <v>-0.3959</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3527</v>
+        <v>-0.1579</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1322</v>
+        <v>-0.238</v>
       </c>
       <c r="V7" t="n">
         <v>-0.6036</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5382</v>
+        <v>0.1161</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2043</v>
+        <v>0.5941</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7425</v>
+        <v>-0.478</v>
       </c>
       <c r="G8" t="n">
         <v>-0.6469</v>
@@ -1078,13 +1078,13 @@
         <v>0.5661</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0611</v>
+        <v>-0.4068</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.2569</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4144</v>
+        <v>-0.1499</v>
       </c>
       <c r="V8" t="n">
         <v>0.6036</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.923</v>
+        <v>-0.8965</v>
       </c>
       <c r="E9" t="n">
         <v>-0.1552</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7677</v>
+        <v>-0.7413</v>
       </c>
       <c r="G9" t="n">
         <v>-0.6343</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2886</v>
+        <v>-0.2622</v>
       </c>
       <c r="T9" t="n">
         <v>-0.1764</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1123</v>
+        <v>-0.0858</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4053</v>
+        <v>-1.255</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7625</v>
+        <v>-0.6651</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6428</v>
+        <v>-0.5899</v>
       </c>
       <c r="G10" t="n">
         <v>-1.1931</v>
@@ -1234,13 +1234,13 @@
         <v>0.1887</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4009</v>
+        <v>-0.2506</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1764</v>
+        <v>-0.0789</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2246</v>
+        <v>-0.1716</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. MARZIALI</t>
+          <t>A. KLEINJAN RODRIGUEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.6144</v>
+        <v>-1.453</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.8228</v>
+        <v>-1.7907</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2084</v>
+        <v>0.3377</v>
       </c>
       <c r="G11" t="n">
-        <v>1.4764</v>
+        <v>-0.157</v>
       </c>
       <c r="H11" t="n">
-        <v>1.5065</v>
+        <v>1.5926</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.0301</v>
+        <v>-1.7496</v>
       </c>
       <c r="J11" t="n">
-        <v>2.8251</v>
+        <v>1.3717</v>
       </c>
       <c r="K11" t="n">
-        <v>1.4267</v>
+        <v>2.4722</v>
       </c>
       <c r="L11" t="n">
-        <v>1.3984</v>
+        <v>-1.1005</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.3487</v>
+        <v>-1.5286</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0798</v>
+        <v>-0.8796</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.4285</v>
+        <v>-0.649</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.2644</v>
+        <v>-0.3774</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.774</v>
+        <v>-2.0757</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5096</v>
+        <v>1.6983</v>
       </c>
       <c r="S11" t="n">
-        <v>0.117</v>
+        <v>-0.9186</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2323</v>
+        <v>-0.7659</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3492</v>
+        <v>-0.1528</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.9434</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.6415999999999999</v>
+        <v>-0.3208</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.3018</v>
+        <v>0.3208</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. KLEINJAN RODRIGUEZ</t>
+          <t>M. MARZIALI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.1274</v>
+        <v>-1.9478</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.2005</v>
+        <v>-1.9975</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0731</v>
+        <v>0.0496</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.157</v>
+        <v>1.4764</v>
       </c>
       <c r="H12" t="n">
-        <v>1.5926</v>
+        <v>1.5065</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.7496</v>
+        <v>-0.0301</v>
       </c>
       <c r="J12" t="n">
-        <v>1.3717</v>
+        <v>2.8251</v>
       </c>
       <c r="K12" t="n">
-        <v>2.4722</v>
+        <v>1.4267</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.1005</v>
+        <v>1.3984</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.5286</v>
+        <v>-1.3487</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.8796</v>
+        <v>0.0798</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.649</v>
+        <v>-1.4285</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.3774</v>
+        <v>-2.2644</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.0757</v>
+        <v>-3.774</v>
       </c>
       <c r="R12" t="n">
-        <v>1.6983</v>
+        <v>1.5096</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.5931</v>
+        <v>-0.2165</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.1758</v>
+        <v>-0.407</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4173</v>
+        <v>0.1905</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-0.9434</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.3208</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="X12" t="n">
-        <v>0.3208</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.4806</v>
+        <v>-4.0807</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.6264</v>
+        <v>-1.7238</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.8543</v>
+        <v>-2.3569</v>
       </c>
       <c r="G13" t="n">
         <v>-1.8186</v>
@@ -1468,13 +1468,13 @@
         <v>1.3209</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6395999999999999</v>
+        <v>0.0396</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0312</v>
+        <v>-0.1286</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6708</v>
+        <v>0.1682</v>
       </c>
       <c r="V13" t="n">
         <v>-2.4904</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.116599999999998</v>
+        <v>8.7044</v>
       </c>
       <c r="E14" t="n">
-        <v>9.339999999999998</v>
+        <v>9.927899999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.2234</v>
+        <v>-1.2235</v>
       </c>
       <c r="G14" t="n">
         <v>6.789300000000001</v>
@@ -1537,7 +1537,7 @@
         <v>-6.8165</v>
       </c>
       <c r="P14" t="n">
-        <v>1.887</v>
+        <v>1.886999999999999</v>
       </c>
       <c r="Q14" t="n">
         <v>-10.3785</v>
@@ -1546,13 +1546,13 @@
         <v>12.2655</v>
       </c>
       <c r="S14" t="n">
-        <v>-4.3148</v>
+        <v>-3.7268</v>
       </c>
       <c r="T14" t="n">
-        <v>-3.9774</v>
+        <v>-3.3895</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3375</v>
+        <v>-0.3373999999999999</v>
       </c>
       <c r="V14" t="n">
         <v>3.754599999999999</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.9919</v>
+        <v>5.4395</v>
       </c>
       <c r="E15" t="n">
-        <v>3.5486</v>
+        <v>4.1332</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4432</v>
+        <v>1.3062</v>
       </c>
       <c r="G15" t="n">
         <v>1.884</v>
@@ -1624,13 +1624,13 @@
         <v>1.887</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6173</v>
+        <v>1.0649</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8078</v>
+        <v>-0.2232</v>
       </c>
       <c r="U15" t="n">
-        <v>1.4251</v>
+        <v>1.2881</v>
       </c>
       <c r="V15" t="n">
         <v>0.6036</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.3754</v>
+        <v>4.4222</v>
       </c>
       <c r="E16" t="n">
-        <v>4.5736</v>
+        <v>4.2813</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1983</v>
+        <v>0.1409</v>
       </c>
       <c r="G16" t="n">
         <v>4.3376</v>
@@ -1702,13 +1702,13 @@
         <v>0.3774</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5849</v>
+        <v>0.6318</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5937</v>
+        <v>0.3014</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.3304</v>
       </c>
       <c r="V16" t="n">
         <v>0.019</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>V. CARLES TEJEDO</t>
+          <t>A. DOMINGUEZ CARRAL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.3822</v>
+        <v>-1.022</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7793</v>
+        <v>-1.3776</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.1615</v>
+        <v>0.3556</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.9415</v>
+        <v>-3.4103</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.7991</v>
+        <v>-3.2869</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1424</v>
+        <v>-0.1234</v>
       </c>
       <c r="J18" t="n">
-        <v>1.4152</v>
+        <v>-0.9846</v>
       </c>
       <c r="K18" t="n">
-        <v>1.1684</v>
+        <v>-2.376</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2468</v>
+        <v>1.3914</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.3566</v>
+        <v>-2.4257</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.9674</v>
+        <v>-0.9109</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3892</v>
+        <v>-1.5148</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>-1.887</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9435</v>
+        <v>1.887</v>
       </c>
       <c r="S18" t="n">
-        <v>1.382</v>
+        <v>0.7771</v>
       </c>
       <c r="T18" t="n">
-        <v>0.9493</v>
+        <v>-0.053</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4327</v>
+        <v>0.8300999999999999</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.8792</v>
+        <v>1.6112</v>
       </c>
       <c r="W18" t="n">
-        <v>0.3018</v>
+        <v>1.547</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.181</v>
+        <v>0.06419999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3987</v>
+        <v>-1.3819</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3834</v>
+        <v>-0.5782</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0154</v>
+        <v>-0.8037</v>
       </c>
       <c r="G19" t="n">
         <v>-1.7324</v>
@@ -1936,13 +1936,13 @@
         <v>1.3209</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5337</v>
+        <v>0.5505</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6647999999999999</v>
+        <v>0.4699</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1311</v>
+        <v>0.0806</v>
       </c>
       <c r="V19" t="n">
         <v>-0.5774</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. DOMINGUEZ CARRAL</t>
+          <t>P. GOMEZ FURONES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4141</v>
+        <v>-1.6312</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.3776</v>
+        <v>-0.4775</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0365</v>
+        <v>-1.1537</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.4103</v>
+        <v>-0.8315</v>
       </c>
       <c r="H20" t="n">
-        <v>-3.2869</v>
+        <v>-0.4829</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1234</v>
+        <v>-0.3486</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.9846</v>
+        <v>-0.5873</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.376</v>
+        <v>0.0211</v>
       </c>
       <c r="L20" t="n">
-        <v>1.3914</v>
+        <v>-0.6084000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.4257</v>
+        <v>-0.2442</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.9109</v>
+        <v>-0.504</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.5148</v>
+        <v>0.2598</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>0.3774</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.887</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.887</v>
+        <v>0.3774</v>
       </c>
       <c r="S20" t="n">
-        <v>0.385</v>
+        <v>0.068</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.053</v>
+        <v>0.1098</v>
       </c>
       <c r="U20" t="n">
-        <v>0.438</v>
+        <v>-0.0417</v>
       </c>
       <c r="V20" t="n">
-        <v>1.6112</v>
+        <v>-1.2452</v>
       </c>
       <c r="W20" t="n">
-        <v>1.547</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.06419999999999999</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. GOMEZ FURONES</t>
+          <t>I. HORRACH SANCHEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7816</v>
+        <v>-1.7754</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.575</v>
+        <v>-1.1198</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2066</v>
+        <v>-0.6556</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.8315</v>
+        <v>-2.2324</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.4829</v>
+        <v>-1.4314</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3486</v>
+        <v>-0.801</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.5873</v>
+        <v>-1.2357</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0211</v>
+        <v>-0.5862000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6084000000000001</v>
+        <v>-0.6496</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.2442</v>
+        <v>-0.9967</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.504</v>
+        <v>-0.8452</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2598</v>
+        <v>-0.1515</v>
       </c>
       <c r="P21" t="n">
-        <v>0.3774</v>
+        <v>0.1887</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.3774</v>
+        <v>0.1887</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0823</v>
+        <v>0.2041</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0123</v>
+        <v>0.1159</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0946</v>
+        <v>0.0882</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.2452</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2452</v>
+        <v>0.06419999999999999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>I. HORRACH SANCHEZ</t>
+          <t>V. CARLES TEJEDO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.1206</v>
+        <v>-1.861</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.4121</v>
+        <v>0.1947</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7085</v>
+        <v>-2.0557</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.2324</v>
+        <v>-0.9415</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.4314</v>
+        <v>-0.7991</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.801</v>
+        <v>-0.1424</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.2357</v>
+        <v>1.4152</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.5862000000000001</v>
+        <v>1.1684</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6496</v>
+        <v>0.2468</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.9967</v>
+        <v>-2.3566</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.8452</v>
+        <v>-1.9674</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1515</v>
+        <v>-0.3892</v>
       </c>
       <c r="P22" t="n">
-        <v>0.1887</v>
+        <v>-0.9435</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="R22" t="n">
-        <v>0.1887</v>
+        <v>0.9435</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1411</v>
+        <v>0.9032</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1764</v>
+        <v>0.3647</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0353</v>
+        <v>0.5385</v>
       </c>
       <c r="V22" t="n">
-        <v>0.06419999999999999</v>
+        <v>-0.8792</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.3018</v>
       </c>
       <c r="X22" t="n">
-        <v>0.06419999999999999</v>
+        <v>-1.181</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D. CAMEROS JUAN</t>
+          <t>A. PINTO MEDINA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.6566</v>
+        <v>-3.0468</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.6373</v>
+        <v>-0.9842</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.0193</v>
+        <v>-2.0625</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.9445</v>
+        <v>-3.2325</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.5096</v>
+        <v>-1.3766</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.4349</v>
+        <v>-1.8559</v>
       </c>
       <c r="J23" t="n">
-        <v>0.1734</v>
+        <v>0.0168</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1323</v>
+        <v>-0.0102</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0411</v>
+        <v>0.027</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.1179</v>
+        <v>-3.2493</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.6419</v>
+        <v>-1.3664</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.476</v>
+        <v>-1.8829</v>
       </c>
       <c r="P23" t="n">
         <v>-0.3774</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.9435</v>
+        <v>-1.887</v>
       </c>
       <c r="R23" t="n">
-        <v>0.5661</v>
+        <v>1.5096</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1481</v>
+        <v>0.2234</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1328</v>
+        <v>-0.3593</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0153</v>
+        <v>0.5826</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.4829</v>
+        <v>0.3398</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.2452</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.4829</v>
+        <v>-0.9054</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. PINTO MEDINA</t>
+          <t>D. CAMEROS JUAN</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.6746</v>
+        <v>-3.4762</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.374</v>
+        <v>-0.6373</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.3006</v>
+        <v>-2.8388</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.2325</v>
+        <v>-1.9445</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.3766</v>
+        <v>-1.5096</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.8559</v>
+        <v>-0.4349</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0168</v>
+        <v>0.1734</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.0102</v>
+        <v>0.1323</v>
       </c>
       <c r="L24" t="n">
-        <v>0.027</v>
+        <v>0.0411</v>
       </c>
       <c r="M24" t="n">
-        <v>-3.2493</v>
+        <v>-2.1179</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.3664</v>
+        <v>-1.6419</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.8829</v>
+        <v>-0.476</v>
       </c>
       <c r="P24" t="n">
         <v>-0.3774</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.887</v>
+        <v>-0.9435</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5096</v>
+        <v>0.5661</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.4045</v>
+        <v>0.3286</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.749</v>
+        <v>0.1328</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3445</v>
+        <v>0.1958</v>
       </c>
       <c r="V24" t="n">
-        <v>0.3398</v>
+        <v>-1.4829</v>
       </c>
       <c r="W24" t="n">
-        <v>1.2452</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.9054</v>
+        <v>-1.4829</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.9399</v>
+        <v>-4.3692</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.8035</v>
+        <v>-4.0958</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.1364</v>
+        <v>-0.2734</v>
       </c>
       <c r="G25" t="n">
         <v>-0.5708</v>
@@ -2404,13 +2404,13 @@
         <v>1.3209</v>
       </c>
       <c r="S25" t="n">
-        <v>1.2915</v>
+        <v>0.8622</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.2294</v>
+        <v>-0.5217000000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>1.5209</v>
+        <v>1.3839</v>
       </c>
       <c r="V25" t="n">
         <v>-2.2076</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-8.116200000000001</v>
+        <v>-6.817200000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>1.223399999999999</v>
+        <v>1.223600000000002</v>
       </c>
       <c r="F26" t="n">
-        <v>-9.339899999999998</v>
+        <v>-8.040699999999999</v>
       </c>
       <c r="G26" t="n">
         <v>-6.789499999999999</v>
@@ -2452,7 +2452,7 @@
         <v>-7.2235</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4339999999999996</v>
+        <v>0.4339999999999997</v>
       </c>
       <c r="J26" t="n">
         <v>11.058</v>
@@ -2482,13 +2482,13 @@
         <v>10.3785</v>
       </c>
       <c r="S26" t="n">
-        <v>4.3146</v>
+        <v>5.613799999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>0.3373000000000001</v>
+        <v>0.3372999999999999</v>
       </c>
       <c r="U26" t="n">
-        <v>3.9773</v>
+        <v>5.2765</v>
       </c>
       <c r="V26" t="n">
         <v>-3.7545</v>
